--- a/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
+++ b/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="11400" windowHeight="5895"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист_123" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" refMode="R1C1"/>
 </workbook>
@@ -27,11 +27,11 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (06.12.2024 3:22:09): 
+          <t>Бюджетирование1 (03.03.2026 18:15:45): 
 Первая ячейка
-Бюджетирование1 (06.12.2024 3:22:10): 
+Бюджетирование1 (03.03.2026 18:15:45): 
 Первая ячейка 2
-Бюджетирование1 (06.12.2024 3:22:15): 
+Бюджетирование1 (03.03.2026 18:15:47): 
 Первая ячейка 3</t>
         </r>
       </text>
@@ -44,7 +44,7 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (06.12.2024 3:22:09): 
+          <t>Бюджетирование1 (03.03.2026 18:15:45): 
 Последняя ячейка</t>
         </r>
       </text>
